--- a/완제품 해외담당.xlsx
+++ b/완제품 해외담당.xlsx
@@ -1187,14 +1187,14 @@
       </c>
     </row>
     <row r="26" spans="1:2">
-      <c r="A26" t="s">
-        <v>4</v>
-      </c>
       <c r="B26" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="27" spans="1:2">
+      <c r="A27" t="s">
+        <v>3</v>
+      </c>
       <c r="B27" t="s">
         <v>37</v>
       </c>
